--- a/data/trans_orig/P63-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P63-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60229</t>
+          <t>59820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89287</t>
+          <t>88362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77331</t>
+          <t>76867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107505</t>
+          <t>107736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145009</t>
+          <t>147397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187290</t>
+          <t>191293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227308</t>
+          <t>228233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256366</t>
+          <t>256775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216506</t>
+          <t>216275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246680</t>
+          <t>247144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>453316</t>
+          <t>449313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>495597</t>
+          <t>493209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125756</t>
+          <t>123608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147398</t>
+          <t>147379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181636</t>
+          <t>182641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213107</t>
+          <t>214314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315555</t>
+          <t>312616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353913</t>
+          <t>352507</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28685</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50327</t>
+          <t>52475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69836</t>
+          <t>68629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101307</t>
+          <t>100302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105114</t>
+          <t>106520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143472</t>
+          <t>146411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58751</t>
+          <t>59493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>69690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>220109</t>
+          <t>222392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>258807</t>
+          <t>259811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286284</t>
+          <t>285646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>328038</t>
+          <t>325539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126390</t>
+          <t>125386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165088</t>
+          <t>162805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128214</t>
+          <t>130713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169968</t>
+          <t>170606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66527</t>
+          <t>66215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78315</t>
+          <t>78644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150852</t>
+          <t>152448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188753</t>
+          <t>188551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222954</t>
+          <t>224150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265282</t>
+          <t>264619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155975</t>
+          <t>156177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193876</t>
+          <t>192280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160272</t>
+          <t>160935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202600</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214990</t>
+          <t>217145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133480</t>
+          <t>133049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169592</t>
+          <t>169699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>349853</t>
+          <t>351260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393533</t>
+          <t>393376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,21%</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169242</t>
+          <t>169135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205354</t>
+          <t>205785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166729</t>
+          <t>166886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210409</t>
+          <t>209002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>281851</t>
+          <t>281746</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>289130</t>
+          <t>289131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115790</t>
+          <t>116667</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>150516</t>
+          <t>150409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>397442</t>
+          <t>398511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>443193</t>
+          <t>443293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188797</t>
+          <t>188904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223523</t>
+          <t>222646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186136</t>
+          <t>186036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>231887</t>
+          <t>230818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202500</t>
+          <t>202891</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98668</t>
+          <t>98228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134122</t>
+          <t>137197</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>298910</t>
+          <t>293949</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>345805</t>
+          <t>344208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>199786</t>
+          <t>196711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>235240</t>
+          <t>235680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195515</t>
+          <t>197112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>242410</t>
+          <t>247371</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1032624</t>
+          <t>1034857</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1092730</t>
+          <t>1096006</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1053538</t>
+          <t>1052363</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1148063</t>
+          <t>1149567</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2106175</t>
+          <t>2108241</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2228177</t>
+          <t>2224077</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>267409</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>330791</t>
+          <t>328558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1200871</t>
+          <t>1199367</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1295396</t>
+          <t>1296571</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1484172</t>
+          <t>1488272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1606174</t>
+          <t>1604108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137830</t>
+          <t>137761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175104</t>
+          <t>174139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83986</t>
+          <t>86152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118648</t>
+          <t>119307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232299</t>
+          <t>231067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>286784</t>
+          <t>284404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193333</t>
+          <t>194298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230607</t>
+          <t>230676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223781</t>
+          <t>223122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258443</t>
+          <t>256277</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>424082</t>
+          <t>426462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>478567</t>
+          <t>479799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>244256</t>
+          <t>244422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269188</t>
+          <t>269199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>250393</t>
+          <t>249708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>281579</t>
+          <t>279901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>505072</t>
+          <t>502436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>544038</t>
+          <t>541792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32076</t>
+          <t>32065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57008</t>
+          <t>56842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>52143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81651</t>
+          <t>82336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89270</t>
+          <t>91516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128236</t>
+          <t>130872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>245779</t>
+          <t>246952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>322053</t>
+          <t>323679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>355405</t>
+          <t>354534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>573851</t>
+          <t>574381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>608034</t>
+          <t>607958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66821</t>
+          <t>67692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100173</t>
+          <t>98547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67894</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102077</t>
+          <t>101547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230530</t>
+          <t>231223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242808</t>
+          <t>242795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228305</t>
+          <t>224817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264718</t>
+          <t>266464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>464702</t>
+          <t>463087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505943</t>
+          <t>506184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120805</t>
+          <t>119059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157218</t>
+          <t>160706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124448</t>
+          <t>124207</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165689</t>
+          <t>167304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>265638</t>
+          <t>265018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164802</t>
+          <t>166354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205395</t>
+          <t>207434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>430437</t>
+          <t>430713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>478279</t>
+          <t>477784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168618</t>
+          <t>166579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209211</t>
+          <t>207659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166826</t>
+          <t>167321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214668</t>
+          <t>214392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>299772</t>
+          <t>300560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>155107</t>
+          <t>158772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194098</t>
+          <t>193678</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>457039</t>
+          <t>458771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>502535</t>
+          <t>503457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>156090</t>
+          <t>156510</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195081</t>
+          <t>191416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154423</t>
+          <t>153501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199919</t>
+          <t>198187</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>247701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249851</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147583</t>
+          <t>148286</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188534</t>
+          <t>189077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>392691</t>
+          <t>396055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>441224</t>
+          <t>443919</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>200445</t>
+          <t>199902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>241396</t>
+          <t>240693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197606</t>
+          <t>194911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>246139</t>
+          <t>242775</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1696224</t>
+          <t>1698001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1758590</t>
+          <t>1755582</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1433281</t>
+          <t>1434320</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1535756</t>
+          <t>1535416</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3155172</t>
+          <t>3146761</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3284902</t>
+          <t>3278176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>237393</t>
+          <t>240401</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>299759</t>
+          <t>297982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1059647</t>
+          <t>1059987</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1162122</t>
+          <t>1161083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1306484</t>
+          <t>1313210</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1436214</t>
+          <t>1444625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77037</t>
+          <t>78096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109489</t>
+          <t>111137</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64159</t>
+          <t>64404</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96080</t>
+          <t>92777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149677</t>
+          <t>150533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193964</t>
+          <t>196093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226461</t>
+          <t>224813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258913</t>
+          <t>257854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207820</t>
+          <t>211123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239741</t>
+          <t>239496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>445886</t>
+          <t>443757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>490173</t>
+          <t>489317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196840</t>
+          <t>194706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>218514</t>
+          <t>217721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204942</t>
+          <t>205708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233523</t>
+          <t>233800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>410248</t>
+          <t>408928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445806</t>
+          <t>445351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>26623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47504</t>
+          <t>49638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54357</t>
+          <t>54080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82938</t>
+          <t>82172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86417</t>
+          <t>86872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121975</t>
+          <t>123295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203727</t>
+          <t>202691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>256008</t>
+          <t>255393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285819</t>
+          <t>286036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462313</t>
+          <t>463324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>493729</t>
+          <t>494304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58153</t>
+          <t>57936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87964</t>
+          <t>88579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59752</t>
+          <t>59177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91168</t>
+          <t>90157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>269381</t>
+          <t>268657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277331</t>
+          <t>277327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251680</t>
+          <t>251036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289950</t>
+          <t>289990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>521875</t>
+          <t>524996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>566830</t>
+          <t>567794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113845</t>
+          <t>113805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152115</t>
+          <t>152759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115285</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160240</t>
+          <t>157119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>303346</t>
+          <t>303113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>311188</t>
+          <t>311163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196726</t>
+          <t>195295</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238220</t>
+          <t>238125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>501261</t>
+          <t>501682</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>548326</t>
+          <t>549306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150436</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191930</t>
+          <t>193361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152522</t>
+          <t>151542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>199587</t>
+          <t>199166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>327172</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>329140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166083</t>
+          <t>167928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205758</t>
+          <t>206542</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>492975</t>
+          <t>490153</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>540310</t>
+          <t>539703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>163742</t>
+          <t>162958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203417</t>
+          <t>201572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158330</t>
+          <t>158937</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205665</t>
+          <t>208487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>254575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144441</t>
+          <t>145744</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190477</t>
+          <t>187508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>393406</t>
+          <t>397023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>449518</t>
+          <t>449850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207197</t>
+          <t>210166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>253233</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>204359</t>
+          <t>204027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>260471</t>
+          <t>256854</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1641647</t>
+          <t>1642828</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1707558</t>
+          <t>1708648</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1361163</t>
+          <t>1361597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1460841</t>
+          <t>1461381</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3028941</t>
+          <t>3026097</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3155190</t>
+          <t>3157114</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>258099</t>
+          <t>257009</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>324010</t>
+          <t>322829</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1034536</t>
+          <t>1033996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1134214</t>
+          <t>1133780</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1305844</t>
+          <t>1303920</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1432093</t>
+          <t>1434937</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023 (tasa de respuesta: 98,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45059</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97348</t>
+          <t>95832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23673</t>
+          <t>24086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48707</t>
+          <t>50499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76290</t>
+          <t>75632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>134223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181654</t>
+          <t>183170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233943</t>
+          <t>234755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159204</t>
+          <t>157412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184238</t>
+          <t>183825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>353694</t>
+          <t>352690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>410623</t>
+          <t>411281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44883</t>
+          <t>46249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>63034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93411</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117964</t>
+          <t>117418</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147007</t>
+          <t>145050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176728</t>
+          <t>177087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33191</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57744</t>
+          <t>59246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>42708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72788</t>
+          <t>74745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66154</t>
+          <t>66146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144083</t>
+          <t>144448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161753</t>
+          <t>162053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214546</t>
+          <t>214014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233143</t>
+          <t>232467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -10474,7 +10474,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26391</t>
+          <t>26091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>28684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46605</t>
+          <t>47137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119459</t>
+          <t>119495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131730</t>
+          <t>131779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162372</t>
+          <t>162601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185770</t>
+          <t>187705</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287217</t>
+          <t>286283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315331</t>
+          <t>315431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71841</t>
+          <t>69906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95239</t>
+          <t>95010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78021</t>
+          <t>77921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106135</t>
+          <t>107069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>252241</t>
+          <t>251265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260049</t>
+          <t>260040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>215586</t>
+          <t>218370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>241445</t>
+          <t>243595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>473038</t>
+          <t>472241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>503043</t>
+          <t>501174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93896</t>
+          <t>91746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119755</t>
+          <t>116971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93064</t>
+          <t>94933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123069</t>
+          <t>123866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>345715</t>
+          <t>345538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>350222</t>
+          <t>350228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>395411</t>
+          <t>395348</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>541026</t>
+          <t>536846</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>774436</t>
+          <t>774785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>872642</t>
+          <t>869936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193480</t>
+          <t>193543</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66994</t>
+          <t>69700</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165200</t>
+          <t>164851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277218</t>
+          <t>277186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210089</t>
+          <t>210471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239353</t>
+          <t>239968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>487233</t>
+          <t>487266</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>521841</t>
+          <t>520929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>184408</t>
+          <t>183793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>213672</t>
+          <t>213290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>183080</t>
+          <t>183992</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217688</t>
+          <t>217655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1161421</t>
+          <t>1159417</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1250838</t>
+          <t>1249434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1296788</t>
+          <t>1291436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1580121</t>
+          <t>1604964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2512451</t>
+          <t>2513521</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2789783</t>
+          <t>2788307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>198223</t>
+          <t>199627</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>287640</t>
+          <t>289644</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>572692</t>
+          <t>547849</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>856025</t>
+          <t>861377</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>812092</t>
+          <t>813568</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1089424</t>
+          <t>1088354</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P63-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P63-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>89939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76867</t>
+          <t>76190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107736</t>
+          <t>110175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147397</t>
+          <t>145779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191293</t>
+          <t>189573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228233</t>
+          <t>226656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256775</t>
+          <t>256783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216275</t>
+          <t>213836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247144</t>
+          <t>247821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>449313</t>
+          <t>451033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>493209</t>
+          <t>494827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123608</t>
+          <t>126163</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147379</t>
+          <t>146979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182641</t>
+          <t>180709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>214314</t>
+          <t>212776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>312616</t>
+          <t>313732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352507</t>
+          <t>354385</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52475</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68629</t>
+          <t>70167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100302</t>
+          <t>102234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106520</t>
+          <t>104642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146411</t>
+          <t>145295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59493</t>
+          <t>60016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69690</t>
+          <t>69845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>222392</t>
+          <t>221572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259811</t>
+          <t>258426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285646</t>
+          <t>286244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325539</t>
+          <t>327809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125386</t>
+          <t>126771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162805</t>
+          <t>163625</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130713</t>
+          <t>128443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170606</t>
+          <t>170008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66215</t>
+          <t>66849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>78768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152448</t>
+          <t>152120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188551</t>
+          <t>186889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224150</t>
+          <t>223689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264619</t>
+          <t>264993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156177</t>
+          <t>157839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192280</t>
+          <t>192608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160935</t>
+          <t>160561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>201865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217145</t>
+          <t>216108</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133049</t>
+          <t>133302</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169699</t>
+          <t>169847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>351260</t>
+          <t>350326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393376</t>
+          <t>392254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169135</t>
+          <t>168987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205785</t>
+          <t>205532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166886</t>
+          <t>168008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209002</t>
+          <t>209936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>281746</t>
+          <t>282554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>289131</t>
+          <t>289118</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>116667</t>
+          <t>116223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>150409</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>398511</t>
+          <t>397645</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>443293</t>
+          <t>442817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188904</t>
+          <t>188709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222646</t>
+          <t>223090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186036</t>
+          <t>186512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>230818</t>
+          <t>231684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202891</t>
+          <t>202628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98228</t>
+          <t>97406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137197</t>
+          <t>135253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>293949</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>344208</t>
+          <t>346729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>196711</t>
+          <t>198655</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>235680</t>
+          <t>236502</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197112</t>
+          <t>194591</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>247371</t>
+          <t>242788</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1034857</t>
+          <t>1037410</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1096006</t>
+          <t>1097737</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1052363</t>
+          <t>1049832</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1149567</t>
+          <t>1146176</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2108241</t>
+          <t>2105268</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2224077</t>
+          <t>2228217</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>267409</t>
+          <t>265678</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>328558</t>
+          <t>326005</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1199367</t>
+          <t>1202758</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1296571</t>
+          <t>1299102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1488272</t>
+          <t>1484132</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1604108</t>
+          <t>1607081</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137761</t>
+          <t>136289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174139</t>
+          <t>174022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86152</t>
+          <t>86495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119307</t>
+          <t>121686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231067</t>
+          <t>232914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284404</t>
+          <t>284849</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194298</t>
+          <t>194415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230676</t>
+          <t>232148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223122</t>
+          <t>220743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256277</t>
+          <t>255934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426462</t>
+          <t>426017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>479799</t>
+          <t>477952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>244422</t>
+          <t>244906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269199</t>
+          <t>269103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>249708</t>
+          <t>249797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>279901</t>
+          <t>279185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>502436</t>
+          <t>503744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>541792</t>
+          <t>542878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32065</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56842</t>
+          <t>56358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52143</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82336</t>
+          <t>82247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91516</t>
+          <t>90430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130872</t>
+          <t>129564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>246952</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>323679</t>
+          <t>323362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>354534</t>
+          <t>355636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>574381</t>
+          <t>573136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>607542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67692</t>
+          <t>66590</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98547</t>
+          <t>98864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67970</t>
+          <t>68386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101547</t>
+          <t>102792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231223</t>
+          <t>231184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242795</t>
+          <t>243743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224817</t>
+          <t>226428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266464</t>
+          <t>263741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>463087</t>
+          <t>464162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>506184</t>
+          <t>508247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119059</t>
+          <t>121782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160706</t>
+          <t>159095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124207</t>
+          <t>122144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167304</t>
+          <t>166229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>265018</t>
+          <t>265894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166354</t>
+          <t>166219</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207434</t>
+          <t>207312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>430713</t>
+          <t>430243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>477784</t>
+          <t>477330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166579</t>
+          <t>166701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207659</t>
+          <t>207794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167321</t>
+          <t>167775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214392</t>
+          <t>214862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>300560</t>
+          <t>299453</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>158772</t>
+          <t>157205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193678</t>
+          <t>196266</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>458771</t>
+          <t>457724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>503457</t>
+          <t>504775</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>156510</t>
+          <t>153922</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>191416</t>
+          <t>192983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153501</t>
+          <t>152183</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198187</t>
+          <t>199234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148286</t>
+          <t>148544</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189077</t>
+          <t>187502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396055</t>
+          <t>393135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>443919</t>
+          <t>442865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>199902</t>
+          <t>201477</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>240693</t>
+          <t>240435</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>194911</t>
+          <t>195965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>242775</t>
+          <t>245695</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1698001</t>
+          <t>1692782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1755582</t>
+          <t>1755327</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1434320</t>
+          <t>1436040</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1535416</t>
+          <t>1537839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3146761</t>
+          <t>3147525</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3278176</t>
+          <t>3275217</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>240401</t>
+          <t>240656</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297982</t>
+          <t>303201</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1059987</t>
+          <t>1057564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1161083</t>
+          <t>1159363</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1313210</t>
+          <t>1316169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1444625</t>
+          <t>1443861</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78096</t>
+          <t>78071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111137</t>
+          <t>111596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64404</t>
+          <t>64120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92777</t>
+          <t>94316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150533</t>
+          <t>150018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196093</t>
+          <t>195723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224813</t>
+          <t>224354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257854</t>
+          <t>257879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>211123</t>
+          <t>209584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239496</t>
+          <t>239780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443757</t>
+          <t>444127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>489317</t>
+          <t>489832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>196957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217721</t>
+          <t>218489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205708</t>
+          <t>205485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233800</t>
+          <t>233771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>408928</t>
+          <t>412334</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445351</t>
+          <t>446299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>25855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49638</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>54109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82172</t>
+          <t>82395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86872</t>
+          <t>85924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123295</t>
+          <t>119889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>203708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>255393</t>
+          <t>256009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>286036</t>
+          <t>286586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>463324</t>
+          <t>463457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>494304</t>
+          <t>493927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57936</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88579</t>
+          <t>87963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90157</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>268657</t>
+          <t>268126</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277327</t>
+          <t>277332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251036</t>
+          <t>251212</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289990</t>
+          <t>289965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>524996</t>
+          <t>524151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>567794</t>
+          <t>565726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113805</t>
+          <t>113830</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152759</t>
+          <t>152583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114321</t>
+          <t>116389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157119</t>
+          <t>157964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>303113</t>
+          <t>302945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>311163</t>
+          <t>311177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195295</t>
+          <t>196197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238125</t>
+          <t>236875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>501682</t>
+          <t>502135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>549306</t>
+          <t>552780</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150531</t>
+          <t>151781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193361</t>
+          <t>192459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151542</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>199166</t>
+          <t>198713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>167928</t>
+          <t>167407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>206542</t>
+          <t>207070</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>490153</t>
+          <t>492730</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>539703</t>
+          <t>540332</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162958</t>
+          <t>162430</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201572</t>
+          <t>202093</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158937</t>
+          <t>158308</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208487</t>
+          <t>205910</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145744</t>
+          <t>143973</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187508</t>
+          <t>188522</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>397023</t>
+          <t>396122</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>449850</t>
+          <t>450966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>210166</t>
+          <t>209152</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>251930</t>
+          <t>253701</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>204027</t>
+          <t>202911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256854</t>
+          <t>257755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1642828</t>
+          <t>1647772</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1708648</t>
+          <t>1708749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1361597</t>
+          <t>1363543</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1461381</t>
+          <t>1461270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3026097</t>
+          <t>3027509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3157114</t>
+          <t>3153572</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>257009</t>
+          <t>256908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>322829</t>
+          <t>317885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1033996</t>
+          <t>1034107</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1133780</t>
+          <t>1131834</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1303920</t>
+          <t>1307462</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1434937</t>
+          <t>1433525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68501</t>
+          <t>70535</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>49770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95832</t>
+          <t>96091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>44821</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50499</t>
+          <t>63156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103839</t>
+          <t>115356</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75632</t>
+          <t>89625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134223</t>
+          <t>147320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>210501</t>
+          <t>204458</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183170</t>
+          <t>178902</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234755</t>
+          <t>225223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>172574</t>
+          <t>199747</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157412</t>
+          <t>181412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183825</t>
+          <t>213218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>383074</t>
+          <t>404204</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>352690</t>
+          <t>372240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>411281</t>
+          <t>429935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>82,75%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>279002</t>
+          <t>274993</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>279002</t>
+          <t>274993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>279002</t>
+          <t>274993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>207911</t>
+          <t>244568</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207911</t>
+          <t>244568</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207911</t>
+          <t>244568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>486913</t>
+          <t>519560</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>486913</t>
+          <t>519560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>486913</t>
+          <t>519560</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56101</t>
+          <t>61249</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46249</t>
+          <t>50842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>69305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>106011</t>
+          <t>122023</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91909</t>
+          <t>106038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117418</t>
+          <t>133298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>162112</t>
+          <t>183273</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>163972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177087</t>
+          <t>198262</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45144</t>
+          <t>51926</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>40651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>67911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>66865</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42708</t>
+          <t>51876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74745</t>
+          <t>86166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68640</t>
+          <t>76188</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68640</t>
+          <t>76188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68640</t>
+          <t>76188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>151155</t>
+          <t>173949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>151155</t>
+          <t>173949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>151155</t>
+          <t>173949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>219795</t>
+          <t>250138</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>219795</t>
+          <t>250138</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>219795</t>
+          <t>250138</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,27 +10351,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70886</t>
+          <t>78359</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66146</t>
+          <t>73011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>80498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>153363</t>
+          <t>175190</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144448</t>
+          <t>164379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162053</t>
+          <t>184963</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>224249</t>
+          <t>253550</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214014</t>
+          <t>242280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232467</t>
+          <t>264123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -10474,12 +10474,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>46005</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43696</t>
+          <t>56816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36902</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>37571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47137</t>
+          <t>59414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>80498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>80498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>80498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>188144</t>
+          <t>221195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>188144</t>
+          <t>221195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>188144</t>
+          <t>221195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>261151</t>
+          <t>301694</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>261151</t>
+          <t>301694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261151</t>
+          <t>301694</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>127010</t>
+          <t>141297</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119495</t>
+          <t>132948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131779</t>
+          <t>146246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>175006</t>
+          <t>192908</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162601</t>
+          <t>180339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187705</t>
+          <t>204775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>302016</t>
+          <t>334205</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286283</t>
+          <t>318625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315431</t>
+          <t>348546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>17251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>82605</t>
+          <t>86623</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69906</t>
+          <t>74756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95010</t>
+          <t>99192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91336</t>
+          <t>95525</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77921</t>
+          <t>81184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107069</t>
+          <t>111105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>257611</t>
+          <t>279531</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>257611</t>
+          <t>279531</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>257611</t>
+          <t>279531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>393352</t>
+          <t>429730</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>393352</t>
+          <t>429730</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>393352</t>
+          <t>429730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>257354</t>
+          <t>274811</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251265</t>
+          <t>268329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260040</t>
+          <t>277054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>230747</t>
+          <t>258546</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>218370</t>
+          <t>243792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243595</t>
+          <t>271111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>488101</t>
+          <t>533357</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>472241</t>
+          <t>515498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>501174</t>
+          <t>548367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>104594</t>
+          <t>114197</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91746</t>
+          <t>101632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116971</t>
+          <t>128951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>108006</t>
+          <t>117712</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94933</t>
+          <t>102702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123866</t>
+          <t>135571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>260766</t>
+          <t>278325</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>260766</t>
+          <t>278325</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>260766</t>
+          <t>278325</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>335341</t>
+          <t>372743</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>335341</t>
+          <t>372743</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>335341</t>
+          <t>372743</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>596107</t>
+          <t>651069</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>596107</t>
+          <t>651069</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>596107</t>
+          <t>651069</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>348675</t>
+          <t>385317</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>345538</t>
+          <t>382330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>350228</t>
+          <t>386892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>466496</t>
+          <t>287689</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>395348</t>
+          <t>273923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>536846</t>
+          <t>301195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>815171</t>
+          <t>673006</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>774785</t>
+          <t>657396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>869936</t>
+          <t>688509</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>122395</t>
+          <t>129829</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>116323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193543</t>
+          <t>143595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>124465</t>
+          <t>131926</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69700</t>
+          <t>116423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164851</t>
+          <t>147536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>350745</t>
+          <t>387414</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>350745</t>
+          <t>387414</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>350745</t>
+          <t>387414</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>588891</t>
+          <t>417518</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>588891</t>
+          <t>417518</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>588891</t>
+          <t>417518</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>939636</t>
+          <t>804932</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>939636</t>
+          <t>804932</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>939636</t>
+          <t>804932</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,27 +11723,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>280027</t>
+          <t>307203</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277186</t>
+          <t>303865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>224483</t>
+          <t>246513</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210471</t>
+          <t>229935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239968</t>
+          <t>263289</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>504509</t>
+          <t>553717</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>487266</t>
+          <t>534667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520929</t>
+          <t>572016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>199278</t>
+          <t>215955</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>183793</t>
+          <t>199179</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>213290</t>
+          <t>232533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>200412</t>
+          <t>217133</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>183992</t>
+          <t>198834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217655</t>
+          <t>236183</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423761</t>
+          <t>462468</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423761</t>
+          <t>462468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423761</t>
+          <t>462468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>704921</t>
+          <t>770850</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>704921</t>
+          <t>770850</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>704921</t>
+          <t>770850</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1208554</t>
+          <t>1318771</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1159417</t>
+          <t>1274910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1249434</t>
+          <t>1359404</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1391442</t>
+          <t>1327691</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1291436</t>
+          <t>1287488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1604964</t>
+          <t>1369894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2599997</t>
+          <t>2646462</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2513521</t>
+          <t>2585898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2788307</t>
+          <t>2706725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>199627</t>
+          <t>196595</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>289644</t>
+          <t>281089</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>547849</t>
+          <t>802078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>861377</t>
+          <t>884484</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>813568</t>
+          <t>1021246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1088354</t>
+          <t>1142073</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
